--- a/AAII_Financials/Quarterly/ATO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>ATO</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>879100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1962400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1342600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>737500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>838800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1950500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1176000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>657900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>701500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1647200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1158500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>587600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>662700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1541000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1484000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>722600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>816400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2662600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1012800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>568400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>605600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2233600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>914500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>474900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>493000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1853200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>875600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>443700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>485700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1972400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>877800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>444700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>562200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2108600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>889200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>464900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>526500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>988200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>780200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>433600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>231400</v>
+      </c>
+      <c r="E9" s="3">
         <v>863100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>525800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>239400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>275900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1012500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>441100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>214700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>208700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>824200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>505200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>193300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>239600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>860900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>923300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>396300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>431500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1565000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>530300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>283300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>271300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1157100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>426900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>198100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>175500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>914800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>449100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>191400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>195900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1101900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>480800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>207000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>276000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1284500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>496000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>233500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>242900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>559700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>436200</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>503200</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>647700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1099300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>816800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>498000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>562800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>938000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>734900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>443200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>492800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>823000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>653300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>394400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>423100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>680000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>560700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>326300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>384900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1097600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>482500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>285100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>334300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1076500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>487600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>276800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>317500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>938400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>426500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>252300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>289800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>870500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>397000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>237700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>286200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>824100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>393200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>231400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>283600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>428500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>344000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>-69600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1490,11 +1510,11 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-200</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1502,30 +1522,30 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>-2800</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1000</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1601,130 +1621,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>201500</v>
+      </c>
+      <c r="E15" s="3">
         <v>195700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>194600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>185700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>185800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>182800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>180500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>173500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>166800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>165100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>164600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>159300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>150700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>148300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>146000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>140200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>134200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>261200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>127900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>124700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>119300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>233900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>115300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>111700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>107100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>211000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>105100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>100900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>97700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>192800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>96100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>92700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>90700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>177800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>88400</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>84800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>80000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>77700</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>77000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>551800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1190800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>821000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>511100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>579800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1314700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>709600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>467700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>476000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1091000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>754200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>455500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>489100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1114000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1162800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>617200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>661800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2001600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>736900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>477400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>472200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1552900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>615600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>374100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>354000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1269000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>622800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>354000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>363500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1438300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>641300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>355100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>439300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1598100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>647100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>373100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>385800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>703000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>570300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>349200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>327200</v>
+      </c>
+      <c r="E18" s="3">
         <v>771600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>521600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>226400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>259000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>635800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>466400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>190300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>225500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>556300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>404300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>132200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>173600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>426900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>321200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>105400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>154600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>661000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>275900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>91000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>133400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>680700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>298900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>100800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>139000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>584200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>252800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>89700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>122200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>534100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>236500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>89600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>122900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>510500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>242100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>91800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>140700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>285200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>210000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>84400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-10700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-15400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>16200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-13200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-17300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-17700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>14400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-14600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-11400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-13500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-30300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>21200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>13300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>13900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>8700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-17000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>8900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>6100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>9200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>537900</v>
+      </c>
+      <c r="E21" s="3">
         <v>978000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>731600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>395900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>458000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>835900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>664600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>349300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>407000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>732800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>582400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>321800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>335100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>588400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>488400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>252200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>302100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>936100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>412400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>198700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>258600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>923500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>420200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>210600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>253400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>797100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>362700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>199900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>221500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>723500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>324800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>181200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>211700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>686000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>327900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>173800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>220400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>363700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>286100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>160700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E22" s="3">
         <v>48700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>33400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>41500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>50000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>52900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>42200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>41200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>55400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>51900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>31800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>31300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>37400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>36800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>27800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>26200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>48800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>14500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>48100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>22000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>15500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>19600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>49400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>27200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>28800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>19600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>54800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>27800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>24500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>58800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>31500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>33700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>28500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>26900</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>31000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>303300</v>
+      </c>
+      <c r="E23" s="3">
         <v>733600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>503600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>213100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>230600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>603100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>431200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>159400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>199000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>512200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>365100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>137300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>154100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>402700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>305600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>84100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>141700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>626100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>264700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>59500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>118300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>641400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>282900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>83400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>126700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>536700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>230400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>70200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>104300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>475900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>200900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>64100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>97600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>449400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>208000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>55300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>111900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>259100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>177900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>54300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E24" s="3">
         <v>151700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>38200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>44200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>117500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>79300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>25400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>33400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>80200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>53800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>16300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>45000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>33800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>13100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>51900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>15500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>10800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>15900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>127000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>65200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>18100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>8900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>118400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>51800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>11800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>23800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>103300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>43200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>18600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>26200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>122000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>55800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>19400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>41100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>97000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>63900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>19400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>242700</v>
+      </c>
+      <c r="E26" s="3">
         <v>581900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>403000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>174900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>186400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>485600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>351900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>134000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>165600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>432000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>311300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>118500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>137800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>357700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>271900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>71600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>128500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>574200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>249200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>48700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>102400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>514400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>217700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>65300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>117800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>418300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>178700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>58400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>80500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>372500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>157600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>45500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>71400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>327400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>152200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>35900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>70800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>162000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>114000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>34900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>242600</v>
+      </c>
+      <c r="E27" s="3">
         <v>581700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>402800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>174800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>186300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>485300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>351700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>134000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>165500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>431800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>311100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>118500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>137700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>357500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>271700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>71600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>128500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>573800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>249000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>48700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>102300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>514100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>217500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>65300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>117700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>418000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>178500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>58400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>80400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>372200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>157500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>45500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>71300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>326900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>151900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>35800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>70700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>161800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>113900</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>34800</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3227,17 +3288,17 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3" t="s">
+      <c r="AD29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3245,35 +3306,38 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-6700</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>165700</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>161900</v>
       </c>
-      <c r="AL29" s="3">
-        <v>0</v>
-      </c>
       <c r="AM29" s="3">
         <v>0</v>
       </c>
       <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
         <v>2700</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>11000</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E32" s="3">
         <v>10700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>15400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-16200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>13200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>17300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>17700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-14400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>14600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>11400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>13500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>30300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>13100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-21200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-13300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-13900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-8700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>17000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-9200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>7700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>1000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>242700</v>
+      </c>
+      <c r="E33" s="3">
         <v>581900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>403000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>174900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>186400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>485600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>351900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>134000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>165600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>432000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>311300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>118500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>137800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>357700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>271700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>71600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>128500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>573800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>249000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>48700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>102300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>514100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>217500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>65300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>117700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>418000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>178500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>58400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>80400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>372200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>157500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>38700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>71100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>492600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>313800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>35800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>70700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>164500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>124900</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>34200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>242700</v>
+      </c>
+      <c r="E35" s="3">
         <v>581900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>403000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>174900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>186400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>485600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>351900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>134000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>165600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>432000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>311300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>118500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>137800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>357700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>271700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>71600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>128500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>573800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>249000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>48700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>102300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>514100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>217500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>65300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>117700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>418000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>178500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>58400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>80400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>372200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>157500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>38700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>71100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>492600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>313800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>35800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>70700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>164500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>124900</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>34200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>521000</v>
+      </c>
+      <c r="E41" s="3">
         <v>125700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>367000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>202700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>709400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>543500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>584500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>307300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>674600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>262500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>278300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>56200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>95200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>171600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>51600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>328100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>582500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>264000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>116700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>524600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>865300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>457600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>20800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>208100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>320100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>189300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>24600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>46200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>108400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>218200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>71100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>54800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>26400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>69800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>45400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>44600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>47500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4356,38 +4446,38 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>121900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>115000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>117200</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>273600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>258600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>233000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>123700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>95700</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4463,496 +4553,511 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>469500</v>
+      </c>
+      <c r="E43" s="3">
         <v>644600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>731100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>384500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>399500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>660600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>628900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>380200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>391600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>596400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>646400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>342600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>330800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>523700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>826400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>363700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>375300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>565200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>514300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>343000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>291100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>469600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>492500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>230600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>236500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>377800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>435600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>230600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>285400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>419600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>478400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>253300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>253500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>407100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>489200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>222300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>250200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>336600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>458800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>431800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>154400</v>
+      </c>
+      <c r="E44" s="3">
         <v>135900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>159500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>191800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>139100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>97300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>153000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>186500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>157900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>144100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>220900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>280100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>211000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>183500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>323700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>357900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>224000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>96300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>220300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>178100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>99500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>50000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>99600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>112000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>84900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>68100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>115300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>130100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>106000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>78100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>146600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>165700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>126000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>89300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>164000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>184700</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>151700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>120000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>163800</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>179100</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>351200</v>
+      </c>
+      <c r="E45" s="3">
         <v>354400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>373700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>192100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>177900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>173300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>339700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>182000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>206300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>169500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>294000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>185800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>165200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>175000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2306100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2274500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2354500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2285000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2275600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2200900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>200200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>235500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>142600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>107900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>72700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>63600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>72000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>72800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>65900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>65100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>69600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>46100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>52400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>55300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>71000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>106300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>62700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>61000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>312200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>239200</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1500800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1262000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1635800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1052700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1552000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1591300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1828100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1132300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1708600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1432400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1679700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>885800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>888900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1073100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3627800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3047700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3281900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3529000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3274200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2838700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1115400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1620400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1192300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>471300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>602200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>829600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>812100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>458000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>503500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>671200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>912700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>478900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>452900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>622700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>778900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>539600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>534400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>563100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>979400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>681700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4962,11 +5067,11 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>114900</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -4974,30 +5079,30 @@
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>202600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>104000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>97200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>84600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>104600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>278800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>250200</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5073,171 +5178,177 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28015600</v>
+      </c>
+      <c r="E48" s="3">
         <v>27069900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26267900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25586900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24378100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23632200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22962000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22453900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21422100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20814600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20319500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19829900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19018300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18445900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17971700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17240200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16556600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16085000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15726800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>15286400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14477700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14039600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13762100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13582500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13106200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12770900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12473900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11787700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11340600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>10971700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>10698200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>10371100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>10071900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9761300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>9518800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>9259200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8924400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>8738500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>8553000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>18411100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>799300</v>
+      </c>
+      <c r="E49" s="3">
         <v>801700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>804100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>806400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>808500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>810100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>811800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>814100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>816300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>818500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>821300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>823500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>824900</v>
-      </c>
-      <c r="P49" s="3">
-        <v>731300</v>
       </c>
       <c r="Q49" s="3">
         <v>731300</v>
@@ -5270,7 +5381,7 @@
         <v>731300</v>
       </c>
       <c r="AA49" s="3">
-        <v>730700</v>
+        <v>731300</v>
       </c>
       <c r="AB49" s="3">
         <v>730700</v>
@@ -5282,7 +5393,7 @@
         <v>730700</v>
       </c>
       <c r="AE49" s="3">
-        <v>730400</v>
+        <v>730700</v>
       </c>
       <c r="AF49" s="3">
         <v>730400</v>
@@ -5294,7 +5405,7 @@
         <v>730400</v>
       </c>
       <c r="AI49" s="3">
-        <v>730100</v>
+        <v>730400</v>
       </c>
       <c r="AJ49" s="3">
         <v>730100</v>
@@ -5306,7 +5417,7 @@
         <v>730100</v>
       </c>
       <c r="AM49" s="3">
-        <v>729700</v>
+        <v>730100</v>
       </c>
       <c r="AN49" s="3">
         <v>729700</v>
@@ -5315,10 +5426,13 @@
         <v>729700</v>
       </c>
       <c r="AP49" s="3">
+        <v>729700</v>
+      </c>
+      <c r="AQ49" s="3">
         <v>727000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1246400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1090600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>259600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>946700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>888700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>188200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1300</v>
       </c>
-      <c r="L52" s="3" t="s">
+      <c r="M52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>497500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>700</v>
       </c>
-      <c r="P52" s="3" t="s">
+      <c r="Q52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1035500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1173800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1085800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>925900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>813500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>752300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2991100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3017500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>790200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>574000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>432000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>385200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>371400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>391200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>306500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>301600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>274400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>294000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>252800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>242100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>236900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>220600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>310300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>330200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>317100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>638700</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31585500</v>
+      </c>
+      <c r="E54" s="3">
         <v>30380100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>29798400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28249500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27712500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>26980400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26497100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25194500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24891300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24004600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23684200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22517000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21771500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21311900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>23366200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22193000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>21655500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21271100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>20545800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>19608700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>19315400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>19408800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16475900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15359000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>14871000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>14716400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>14388100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13367600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12881100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12675000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12615800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11874400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11507600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>11356300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>11264700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>10749600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>10498800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>10361500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>10579200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>10010900</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,195 +6145,199 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>436700</v>
+      </c>
+      <c r="E57" s="3">
         <v>467000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>616900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>381000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>397600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>445200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>453000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>341900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>319400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>367900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>416700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>218200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>327900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>365000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>574700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>496000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>397100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>354000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>398400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>423200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>280400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>263600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>285000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>235800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>200100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>190100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>308100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>265000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>206500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>244000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>301700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>217300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>198200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>230800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>285700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>233100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>164400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>185200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>268600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>196500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>511400</v>
+      </c>
+      <c r="E58" s="3">
         <v>11300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>65600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>44200</v>
-      </c>
-      <c r="K58" s="3">
-        <v>9600</v>
       </c>
       <c r="L58" s="3">
         <v>9600</v>
       </c>
       <c r="M58" s="3">
+        <v>9600</v>
+      </c>
+      <c r="N58" s="3">
         <v>11500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>289200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2201500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2386400</v>
-      </c>
-      <c r="S58" s="3">
-        <v>2201400</v>
       </c>
       <c r="T58" s="3">
         <v>2201400</v>
       </c>
       <c r="U58" s="3">
+        <v>2201400</v>
+      </c>
+      <c r="V58" s="3">
         <v>2401400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2400500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>200400</v>
-      </c>
-      <c r="X58" s="3">
-        <v>200</v>
       </c>
       <c r="Y58" s="3">
         <v>200</v>
@@ -6215,540 +6349,555 @@
         <v>200</v>
       </c>
       <c r="AB58" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC58" s="3">
         <v>200100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>464900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>199900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>125000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>575000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1150800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>694800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>579600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>336800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>447700</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>258600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>920600</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1190700</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1079800</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>896300</v>
+      </c>
+      <c r="E59" s="3">
         <v>780200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>819100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>592900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>712700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>733200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>701900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>541400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>655900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>677700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>742300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>588900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>698900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>746200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>755700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>720200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>660600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>653000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>626700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>686700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>581700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>607500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>512700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>546500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>502400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>543200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>537000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>479500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>494900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>495100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>578800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>547100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>573000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>538700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>336900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>332600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>322700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>390300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>490400</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>512000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1844400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1258500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1447000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1362600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1130500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1198500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1174800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1205900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>984900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1055200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1170500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1352600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1034300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1113000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3531900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3602600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3259100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3208400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3426500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3510400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1062500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>871300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>797800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>782400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>702700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>933400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>845200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1209400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>901400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>864100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1455500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1915100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1466000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1349100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>959400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1013400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>745700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1496100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1949800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1788300</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9812500</v>
+      </c>
+      <c r="E61" s="3">
         <v>9618000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9621900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9238000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8980600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8486300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8490200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8085000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7866500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7526100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7529300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6833700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6642600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6553100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6551800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5760600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5759200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5757600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5555200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4930200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7128500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7316400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5124900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4531800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4531300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4328900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4324300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3529500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3529100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3528700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3084800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2493700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2618300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2617900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3067500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3067000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3066700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2314600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2314200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2188800</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1307400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1311500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1312200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>976300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1225200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1209200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1203800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>900000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1111500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1102400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1099900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>826800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1009400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>989800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3446200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3410700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3369000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3321900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3274600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3261200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3350700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3400200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3340000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3253600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3175500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3149700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3090900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2878500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2808600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2774000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2727300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2695700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2663800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2668000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2674200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2770400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2784700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2715900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2616200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>2570800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16327500</v>
+      </c>
+      <c r="E66" s="3">
         <v>15471400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15515500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14690600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14326700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13842400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13716600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13036800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12708200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12386000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12411000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11646900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11169100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11106700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13529900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12773900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12387300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12287900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12256200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11701800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11541700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11587900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9262700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8567800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8409500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8412000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8260400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7617400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7239100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7166800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7267600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7104500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6748100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6635000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6701100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6850900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>6597100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>6526600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>6880200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>6547800</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5590900</v>
+      </c>
+      <c r="E72" s="3">
         <v>5517300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5104200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4861600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4828200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4780200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4433000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4216600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4208800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4168400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3858100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3666700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3659400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3630000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3378500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3211200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3236200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3202900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2971500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2812700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2846600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2826100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2609700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2471000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2477500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2430300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2261100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2152000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2157300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2138500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1985300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1878100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1871300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1854300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1729300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1467000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1480000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1457000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1339800</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1262500</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15258100</v>
+      </c>
+      <c r="E76" s="3">
         <v>14908700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14282900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13558900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13385800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13138000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12780500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12157700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12183100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11618600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11273200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10870100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10602400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10205200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9836300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9419100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9268200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8983200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8289500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7906900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7773800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7820900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7213200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6791200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6461500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6304400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6127800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5750200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5642000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5508100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5348200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4770000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4759600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4721300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4563600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3898700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3901700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3834900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3699000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3463100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>242700</v>
+      </c>
+      <c r="E81" s="3">
         <v>581900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>403000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>174900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>186400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>485600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>351900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>134000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>165600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>432000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>311300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>118500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>137800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>357700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>271700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>71600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>128500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>573800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>249000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>48700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>102300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>514100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>217500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>65300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>117700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>418000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>178500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>58400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>80400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>372200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>157500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>38700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>71100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>492600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>313800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>35800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>70700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>164500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>124900</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>34200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>184100</v>
+      </c>
+      <c r="E83" s="3">
         <v>181100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>178300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>164700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>166800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>165100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>164600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>159300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>150700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>148300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>146000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>140200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>134200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>133400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>146000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>140200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>134200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>261200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>127900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>124700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>119300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>233900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>115300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>111700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>107100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>211000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>105100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>100900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>97700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>192800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>96100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>92700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>90700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>177800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>88400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>84800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>80000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>77700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>77100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>76400</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>639900</v>
+      </c>
+      <c r="E89" s="3">
         <v>723500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>308100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>348100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>496400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>922900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>282000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>330700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>411200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>746600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>245300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>238200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>328800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2703800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>188900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>48300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>288800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>640500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>61800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>74200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>243800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1402200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>157100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>142500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>261700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>633800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>172400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>159800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>248100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>560800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>164700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>89400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>283900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>751400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>173200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>121500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>193600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>435000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>117000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>165000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1039300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1003600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1033300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-963600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-866900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-839700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-891200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-808000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-713600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-645900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-769700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-722500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-668100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-619700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-795700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-718400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-536000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-505800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-684200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-611600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-512200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-845700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-456800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-530000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-410900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-994700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-529200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-494300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-421600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-777600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-416400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-379100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-394500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-694000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-383200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-324900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-252800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-261400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-298000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>498700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1040400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1035600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-967600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-876100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-828600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-888900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-803700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-709800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-644900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-764400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-718000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-666900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-617900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-792500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-715400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-532600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1182000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-679700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-611300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-506300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-846100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-453600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-525300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-409000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-991200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-528200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-488300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-427000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-768400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-415300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-376300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-399100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-688100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-381400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-309000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-230700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-124500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-392100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-296300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>166200</v>
+      </c>
+      <c r="E96" s="3">
         <v>164100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>160400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>141400</v>
-      </c>
-      <c r="G96" s="3">
-        <v>138400</v>
       </c>
       <c r="H96" s="3">
         <v>138400</v>
       </c>
       <c r="I96" s="3">
+        <v>138400</v>
+      </c>
+      <c r="J96" s="3">
         <v>135500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>126200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>125200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>121700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>119900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>111300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>108300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>106200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-104600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-96700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-95300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-183900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-90400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-82600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-81900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-159300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-79000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-71800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-70600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-140100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-69600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-63700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-61700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-120300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-58700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-54900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-54100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-105900</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-51800</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-48900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-47800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-47600</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-47700</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-44800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>799100</v>
+      </c>
+      <c r="E100" s="3">
         <v>32200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>895300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>109700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>548200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-138600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>887500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>102600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>714100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-123400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>785300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>440900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>301100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2162400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>723700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>390600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-10700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1007300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>765200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>129200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-78200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3092800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>733300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>195500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>35300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>653000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>520500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>306800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>116700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>302200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>455000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>279800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>65000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-18600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>236500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>144100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>61500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-309700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>272300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>398700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-244400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>167700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-509800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>168500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-44300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>280600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-370400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>415500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-21700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>266200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-38900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-37100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-76400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>120000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-276500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-254400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>465800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>147300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-407900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-340700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>844500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>436800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-187300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-112000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>295500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>164700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-21600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-62200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>94600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>204400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-50100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>44700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>28300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-43400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>24400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-18700</v>
       </c>
     </row>
